--- a/excel_templates/methylation_manifest_template.xlsx
+++ b/excel_templates/methylation_manifest_template.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT1899</t>
+          <t>P_5P2QIUH2</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SM7316-11566</t>
+          <t>S_0000012</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AL1549608_T_WGS</t>
+          <t>AL_0000025_T_Methyl</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>MODEL-PARENT-001</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>MODEL-GM-001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>impact trial</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">

--- a/excel_templates/methylation_manifest_template.xlsx
+++ b/excel_templates/methylation_manifest_template.xlsx
@@ -1593,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1632,6 +1632,7 @@
     <col width="24" customWidth="1" min="34" max="34"/>
     <col width="24" customWidth="1" min="35" max="35"/>
     <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1747,77 +1748,82 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>file_platform</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="9">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -1827,26 +1833,23 @@
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$2</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$6</formula1>
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$G$2:$G$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$H$2:$H$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$2</formula1>
+    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1859,7 +1862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,25 +1893,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>organism</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>organism</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -1942,25 +1940,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IlluminaHumanMethylationEPIC</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Homo sapiens</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -1989,20 +1982,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IlluminaHumanMethylationEPICv2</t>
+          <t>Methylation Microarray</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Methylation Microarray</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2029,11 +2017,6 @@
           <t>SHA256</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>IlluminaHumanMethylation450k</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2056,11 +2039,6 @@
           <t>SHA512</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>InfiniumMouseMethylationBeadChip</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2081,11 +2059,6 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ETag</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
         </is>
       </c>
     </row>

--- a/excel_templates/methylation_manifest_template.xlsx
+++ b/excel_templates/methylation_manifest_template.xlsx
@@ -1748,7 +1748,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>file_platform</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">

--- a/excel_templates/methylation_manifest_template.xlsx
+++ b/excel_templates/methylation_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location</t>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1138,20 +1138,24 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1167,17 +1171,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1188,7 +1192,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1196,7 +1200,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1206,14 +1210,10 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>"IDAT"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>IDAT</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1239,18 +1239,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>"IDAT"</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>IDAT</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1258,7 +1262,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1268,22 +1272,18 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
+          <t>529600</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1301,10 +1301,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1312,7 +1316,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
+          <t>MD5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1320,17 +1324,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1341,7 +1345,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1349,24 +1353,20 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>"IlluminaHumanMethylationEPIC", "IlluminaHumanMethylationEPICv2", "IlluminaHumanMethylation450k", "InfiniumMouseMethylationBeadChip", "Unknown"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>IlluminaHumanMethylationEPIC</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>"Methylation", "Methylation Microarray"</t>
+          <t>"IlluminaHumanMethylationEPIC", "IlluminaHumanMethylationEPICv2", "IlluminaHumanMethylation450k", "InfiniumMouseMethylationBeadChip", "Unknown"</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>IlluminaHumanMethylationEPIC</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
+          <t>The sequencing strategy used to generate the data file.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>"True", "False"</t>
+          <t>"Methylation", "Methylation Microarray"</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1458,30 +1458,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1524,14 +1524,10 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1539,50 +1535,87 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Binomial name of organism with full genus name</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>"Homo sapiens", "Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>"Mus musculus"</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:G38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1823,7 +1856,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="11">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -1833,23 +1866,29 @@
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
+    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$D$2:$D$8</formula1>
+    </dataValidation>
     <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$D$2:$D$2</formula1>
+      <formula1>'Lists'!$E$2:$E$2</formula1>
     </dataValidation>
     <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$6</formula1>
+      <formula1>'Lists'!$F$2:$F$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
     <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$3</formula1>
+      <formula1>'Lists'!$H$2:$H$3</formula1>
     </dataValidation>
     <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$3</formula1>
+      <formula1>'Lists'!$I$2:$I$3</formula1>
     </dataValidation>
     <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$3</formula1>
+      <formula1>'Lists'!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$2</formula1>
+      <formula1>'Lists'!$K$2:$K$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1862,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1883,30 +1922,40 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>file_source_platform</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -1930,30 +1979,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>bti_aws</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>IDAT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>IlluminaHumanMethylationEPIC</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Methylation</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -1975,22 +2034,32 @@
           <t>Buffy Coat</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>local_drive</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IlluminaHumanMethylationEPICv2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Methylation Microarray</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2012,9 +2081,19 @@
           <t>Derived Cell Line</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>SHA256</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IlluminaHumanMethylation450k</t>
         </is>
       </c>
     </row>
@@ -2034,9 +2113,19 @@
           <t>Not Available</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cgc</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>SHA512</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>InfiniumMouseMethylationBeadChip</t>
         </is>
       </c>
     </row>
@@ -2056,9 +2145,19 @@
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kids_first</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>ETag</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -2073,6 +2172,11 @@
           <t>Patient Derived Xenograft</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sra</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -2083,6 +2187,11 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Xenograft</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>synapse</t>
         </is>
       </c>
     </row>

--- a/excel_templates/methylation_manifest_template.xlsx
+++ b/excel_templates/methylation_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1614,8 +1614,41 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>"Female", "Male", "Not Reported"</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <autoFilter ref="A1:G39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1626,7 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1666,6 +1699,7 @@
     <col width="24" customWidth="1" min="35" max="35"/>
     <col width="24" customWidth="1" min="36" max="36"/>
     <col width="24" customWidth="1" min="37" max="37"/>
+    <col width="24" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1854,9 +1888,14 @@
           <t>host_organism</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -1890,6 +1929,9 @@
     <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$2</formula1>
     </dataValidation>
+    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$4</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1901,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,6 +2002,11 @@
           <t>host_organism</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2017,6 +2064,11 @@
           <t>Mus musculus</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2064,6 +2116,11 @@
           <t>Mus musculus</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2094,6 +2151,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>IlluminaHumanMethylation450k</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Not Reported</t>
         </is>
       </c>
     </row>
